--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120197270</v>
+        <v>120197246</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>56532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lunglav, Näsvattnet, Sättna, Mpd</t>
+          <t>Tjädertupp, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595666</v>
+        <v>595614</v>
       </c>
       <c r="R2" t="n">
-        <v>6928274</v>
+        <v>6928257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,13 +779,17 @@
           <t>08:30</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca 8 fjädrar av tjädertupp</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120197246</v>
+        <v>120197270</v>
       </c>
       <c r="B3" t="n">
-        <v>56522</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,54 +820,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjädertupp, Näsvattnet, Sättna, Mpd</t>
+          <t>Lunglav, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595614</v>
+        <v>595666</v>
       </c>
       <c r="R3" t="n">
-        <v>6928257</v>
+        <v>6928274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,17 +903,13 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca 8 fjädrar av tjädertupp</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120197246</v>
+        <v>120197270</v>
       </c>
       <c r="B2" t="n">
-        <v>56532</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,54 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjädertupp, Näsvattnet, Sättna, Mpd</t>
+          <t>Lunglav, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595614</v>
+        <v>595666</v>
       </c>
       <c r="R2" t="n">
-        <v>6928257</v>
+        <v>6928274</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -779,17 +770,13 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca 8 fjädrar av tjädertupp</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -808,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120197270</v>
+        <v>120197246</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>56532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,45 +807,54 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lunglav, Näsvattnet, Sättna, Mpd</t>
+          <t>Tjädertupp, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595666</v>
+        <v>595614</v>
       </c>
       <c r="R3" t="n">
-        <v>6928274</v>
+        <v>6928257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,13 +899,17 @@
           <t>08:30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca 8 fjädrar av tjädertupp</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120197270</v>
+        <v>120197246</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>56532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lunglav, Näsvattnet, Sättna, Mpd</t>
+          <t>Tjädertupp, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595666</v>
+        <v>595614</v>
       </c>
       <c r="R2" t="n">
-        <v>6928274</v>
+        <v>6928257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,13 +779,17 @@
           <t>08:30</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca 8 fjädrar av tjädertupp</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120197246</v>
+        <v>120197270</v>
       </c>
       <c r="B3" t="n">
-        <v>56532</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,54 +820,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjädertupp, Näsvattnet, Sättna, Mpd</t>
+          <t>Lunglav, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595614</v>
+        <v>595666</v>
       </c>
       <c r="R3" t="n">
-        <v>6928257</v>
+        <v>6928274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,17 +903,13 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca 8 fjädrar av tjädertupp</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,6 +926,347 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124190248</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56703</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Knärot, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>595770</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6928377</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124190806</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Knärot , Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>595796</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6928382</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124189989</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Knärot, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595770</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6928377</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -928,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124190645</v>
+        <v>124190806</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124190248</v>
+        <v>124189989</v>
       </c>
       <c r="B5" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,33 +1052,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Knärot, Mpd</t>
@@ -1157,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124189989</v>
+        <v>124190248</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,28 +1164,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Knärot, Mpd</t>

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -928,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124190806</v>
+        <v>124189989</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -964,14 +964,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knärot , Mpd</t>
+          <t>Knärot, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595796</v>
+        <v>595770</v>
       </c>
       <c r="R4" t="n">
-        <v>6928382</v>
+        <v>6928377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124189989</v>
+        <v>124190806</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1076,14 +1076,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knärot, Mpd</t>
+          <t>Knärot , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595770</v>
+        <v>595796</v>
       </c>
       <c r="R5" t="n">
-        <v>6928377</v>
+        <v>6928382</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124190806</v>
+        <v>124190248</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,38 +1052,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knärot , Mpd</t>
+          <t>Knärot, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595796</v>
+        <v>595770</v>
       </c>
       <c r="R5" t="n">
-        <v>6928382</v>
+        <v>6928377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124190248</v>
+        <v>124190806</v>
       </c>
       <c r="B6" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,43 +1169,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knärot, Mpd</t>
+          <t>Knärot , Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595770</v>
+        <v>595796</v>
       </c>
       <c r="R6" t="n">
-        <v>6928377</v>
+        <v>6928382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -928,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124189989</v>
+        <v>124190645</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -964,14 +964,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knärot, Mpd</t>
+          <t>Knärot , Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595770</v>
+        <v>595796</v>
       </c>
       <c r="R4" t="n">
-        <v>6928377</v>
+        <v>6928382</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124190806</v>
+        <v>124189989</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1193,14 +1193,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knärot , Mpd</t>
+          <t>Knärot, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595796</v>
+        <v>595770</v>
       </c>
       <c r="R6" t="n">
-        <v>6928382</v>
+        <v>6928377</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -928,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124190645</v>
+        <v>124190248</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,38 +940,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knärot , Mpd</t>
+          <t>Knärot, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595796</v>
+        <v>595770</v>
       </c>
       <c r="R4" t="n">
-        <v>6928382</v>
+        <v>6928377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1040,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124190248</v>
+        <v>124190806</v>
       </c>
       <c r="B5" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,43 +1057,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knärot, Mpd</t>
+          <t>Knärot , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595770</v>
+        <v>595796</v>
       </c>
       <c r="R5" t="n">
-        <v>6928377</v>
+        <v>6928382</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -928,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124190248</v>
+        <v>124190645</v>
       </c>
       <c r="B4" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,43 +940,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knärot, Mpd</t>
+          <t>Knärot , Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595770</v>
+        <v>595796</v>
       </c>
       <c r="R4" t="n">
-        <v>6928377</v>
+        <v>6928382</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1045,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124190806</v>
+        <v>124190248</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,38 +1052,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knärot , Mpd</t>
+          <t>Knärot, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595796</v>
+        <v>595770</v>
       </c>
       <c r="R5" t="n">
-        <v>6928382</v>
+        <v>6928377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -928,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124190645</v>
+        <v>124190806</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -928,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124190806</v>
+        <v>124190645</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124190248</v>
+        <v>124189989</v>
       </c>
       <c r="B5" t="n">
-        <v>56725</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,33 +1052,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Knärot, Mpd</t>
@@ -1157,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124189989</v>
+        <v>124190248</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>56725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,28 +1164,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Knärot, Mpd</t>

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1267,6 +1267,531 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126627891</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595663</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6928234</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126627675</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80111</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595566</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6928292</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126627780</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595620</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6928248</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126627614</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595566</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6928292</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126628071</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>595665</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6928247</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>126627675</v>
       </c>
       <c r="B8" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>126627675</v>
       </c>
       <c r="B8" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>126627891</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>126627780</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>126627614</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>126628071</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21661-2022 artfynd.xlsx
+++ b/artfynd/A 21661-2022 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>126627891</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>126627780</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>126627614</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>126628071</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
